--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblMapper_UserToUserRole.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblMapper_UserToUserRole.xlsx
@@ -5133,6 +5133,195 @@
             <v>4000000000591</v>
           </cell>
         </row>
+        <row r="595">
+          <cell r="B595" t="str">
+            <v>(LDAP) ridwan.nur</v>
+          </cell>
+          <cell r="F595">
+            <v>4000000000592</v>
+          </cell>
+        </row>
+        <row r="596">
+          <cell r="B596" t="str">
+            <v>(LDAP) muhammad.rizal</v>
+          </cell>
+          <cell r="F596">
+            <v>4000000000593</v>
+          </cell>
+        </row>
+        <row r="597">
+          <cell r="B597" t="str">
+            <v>(LDAP) andi.mapasoro</v>
+          </cell>
+          <cell r="F597">
+            <v>4000000000594</v>
+          </cell>
+        </row>
+        <row r="598">
+          <cell r="B598" t="str">
+            <v>(LDAP) taufik.aminudin</v>
+          </cell>
+          <cell r="F598">
+            <v>4000000000595</v>
+          </cell>
+        </row>
+        <row r="599">
+          <cell r="B599" t="str">
+            <v>(LDAP) taufiq.aminudin</v>
+          </cell>
+          <cell r="F599">
+            <v>4000000000596</v>
+          </cell>
+        </row>
+        <row r="600">
+          <cell r="B600" t="str">
+            <v>(LDAP) risty.alawiyah</v>
+          </cell>
+          <cell r="F600">
+            <v>4000000000597</v>
+          </cell>
+        </row>
+        <row r="601">
+          <cell r="B601" t="str">
+            <v>(LDAP) agus.sobar</v>
+          </cell>
+          <cell r="F601">
+            <v>4000000000598</v>
+          </cell>
+        </row>
+        <row r="602">
+          <cell r="B602" t="str">
+            <v>(LDAP) reza.sanjaya</v>
+          </cell>
+          <cell r="F602">
+            <v>4000000000599</v>
+          </cell>
+        </row>
+        <row r="603">
+          <cell r="B603" t="str">
+            <v>(LDAP) kiki.prasetyo</v>
+          </cell>
+          <cell r="F603">
+            <v>4000000000600</v>
+          </cell>
+        </row>
+        <row r="604">
+          <cell r="B604" t="str">
+            <v>(LDAP) ulul.azmi</v>
+          </cell>
+          <cell r="F604">
+            <v>4000000000601</v>
+          </cell>
+        </row>
+        <row r="605">
+          <cell r="B605" t="str">
+            <v>(LDAP) arie.gustaman</v>
+          </cell>
+          <cell r="F605">
+            <v>4000000000602</v>
+          </cell>
+        </row>
+        <row r="606">
+          <cell r="B606" t="str">
+            <v>(LDAP) zulfikar.siregar</v>
+          </cell>
+          <cell r="F606">
+            <v>4000000000603</v>
+          </cell>
+        </row>
+        <row r="607">
+          <cell r="B607" t="str">
+            <v>(LDAP) deby.syahputra</v>
+          </cell>
+          <cell r="F607">
+            <v>4000000000604</v>
+          </cell>
+        </row>
+        <row r="608">
+          <cell r="B608" t="str">
+            <v>(LDAP) Risaldi</v>
+          </cell>
+          <cell r="F608">
+            <v>4000000000605</v>
+          </cell>
+        </row>
+        <row r="609">
+          <cell r="B609" t="str">
+            <v>(LDAP) muhammad.hairul</v>
+          </cell>
+          <cell r="F609">
+            <v>4000000000606</v>
+          </cell>
+        </row>
+        <row r="610">
+          <cell r="B610" t="str">
+            <v>(LDAP) ibrahim.arya</v>
+          </cell>
+          <cell r="F610">
+            <v>4000000000607</v>
+          </cell>
+        </row>
+        <row r="611">
+          <cell r="B611" t="str">
+            <v>(LDAP) m.bilal</v>
+          </cell>
+          <cell r="F611">
+            <v>4000000000608</v>
+          </cell>
+        </row>
+        <row r="612">
+          <cell r="B612" t="str">
+            <v>(LDAP) jamil</v>
+          </cell>
+          <cell r="F612">
+            <v>4000000000609</v>
+          </cell>
+        </row>
+        <row r="613">
+          <cell r="B613" t="str">
+            <v>(LDAP) wiyadianto</v>
+          </cell>
+          <cell r="F613">
+            <v>4000000000610</v>
+          </cell>
+        </row>
+        <row r="614">
+          <cell r="B614" t="str">
+            <v>(LDAP) rahmad.dwifar</v>
+          </cell>
+          <cell r="F614">
+            <v>4000000000611</v>
+          </cell>
+        </row>
+        <row r="615">
+          <cell r="B615" t="str">
+            <v>(LDAP) achmad.sandi</v>
+          </cell>
+          <cell r="F615">
+            <v>4000000000612</v>
+          </cell>
+        </row>
+        <row r="616">
+          <cell r="B616" t="str">
+            <v>(LDAP) andrean.fahrizi</v>
+          </cell>
+          <cell r="F616">
+            <v>4000000000613</v>
+          </cell>
+        </row>
+        <row r="617">
+          <cell r="B617" t="str">
+            <v>(LDAP) amar.abdilah</v>
+          </cell>
+          <cell r="F617">
+            <v>4000000000614</v>
+          </cell>
+        </row>
+        <row r="618">
+          <cell r="F618">
+            <v>4000000000614</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="1"/>
     </sheetDataSet>
@@ -19335,7 +19524,7 @@
         <v>(LDAP) abdul.rachman</v>
       </c>
       <c r="D580" s="7" t="str">
-        <f t="shared" ref="D580:D596" si="27">IF(EXACT(E580, ""), "", IF(EXACT(B580, ""), D579, B580))</f>
+        <f t="shared" ref="D580:D588" si="27">IF(EXACT(E580, ""), "", IF(EXACT(B580, ""), D579, B580))</f>
         <v/>
       </c>
       <c r="E580" s="6"/>
@@ -19365,11 +19554,11 @@
       <c r="E581" s="6"/>
       <c r="F581" s="6"/>
       <c r="H581" s="17">
-        <f t="shared" ref="H581:H592" si="28" xml:space="preserve"> H580 + IF(EXACT(I581, ""), 0, 1)</f>
+        <f t="shared" ref="H581:H589" si="28" xml:space="preserve"> H580 + IF(EXACT(I581, ""), 0, 1)</f>
         <v>96000000000014</v>
       </c>
       <c r="I581" s="16" t="str">
-        <f t="shared" ref="I581:I592" si="29">IF(EXACT(E581, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblMapper_UserToUserRole_SET""(varSystemLoginSession, null, null, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT(D581, ""), "null", D581), "::bigint, ", IF(EXACT(E581, ""), "null", E581), "::bigint, ", IF(EXACT(F581, ""), "null", F581), "::bigint, '0001-01-01 01:01:01+00'::timestamptz, '9999-12-31 23:59:59+00'::timestamptz, null::varchar);"))</f>
+        <f t="shared" ref="I581:I589" si="29">IF(EXACT(E581, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblMapper_UserToUserRole_SET""(varSystemLoginSession, null, null, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT(D581, ""), "null", D581), "::bigint, ", IF(EXACT(E581, ""), "null", E581), "::bigint, ", IF(EXACT(F581, ""), "null", F581), "::bigint, '0001-01-01 01:01:01+00'::timestamptz, '9999-12-31 23:59:59+00'::timestamptz, null::varchar);"))</f>
         <v/>
       </c>
     </row>
@@ -19734,13 +19923,13 @@
       </c>
     </row>
     <row r="597" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B597" s="6" t="str">
+      <c r="B597" s="6">
         <f>IF(EXACT([1]MAIN!$F595, ""), "", [1]MAIN!$F595)</f>
-        <v/>
+        <v>4000000000592</v>
       </c>
       <c r="C597" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F595, ""), "", [1]MAIN!$B595)</f>
-        <v/>
+        <v>(LDAP) ridwan.nur</v>
       </c>
       <c r="D597" s="7" t="str">
         <f t="shared" si="30"/>
@@ -19758,13 +19947,13 @@
       </c>
     </row>
     <row r="598" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B598" s="6" t="str">
+      <c r="B598" s="6">
         <f>IF(EXACT([1]MAIN!$F596, ""), "", [1]MAIN!$F596)</f>
-        <v/>
+        <v>4000000000593</v>
       </c>
       <c r="C598" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F596, ""), "", [1]MAIN!$B596)</f>
-        <v/>
+        <v>(LDAP) muhammad.rizal</v>
       </c>
       <c r="D598" s="7" t="str">
         <f t="shared" si="30"/>
@@ -19782,13 +19971,13 @@
       </c>
     </row>
     <row r="599" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B599" s="6" t="str">
+      <c r="B599" s="6">
         <f>IF(EXACT([1]MAIN!$F597, ""), "", [1]MAIN!$F597)</f>
-        <v/>
+        <v>4000000000594</v>
       </c>
       <c r="C599" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F597, ""), "", [1]MAIN!$B597)</f>
-        <v/>
+        <v>(LDAP) andi.mapasoro</v>
       </c>
       <c r="D599" s="7" t="str">
         <f t="shared" si="30"/>
@@ -19806,13 +19995,13 @@
       </c>
     </row>
     <row r="600" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B600" s="6" t="str">
+      <c r="B600" s="6">
         <f>IF(EXACT([1]MAIN!$F598, ""), "", [1]MAIN!$F598)</f>
-        <v/>
+        <v>4000000000595</v>
       </c>
       <c r="C600" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F598, ""), "", [1]MAIN!$B598)</f>
-        <v/>
+        <v>(LDAP) taufik.aminudin</v>
       </c>
       <c r="D600" s="7" t="str">
         <f t="shared" si="30"/>
@@ -19830,13 +20019,13 @@
       </c>
     </row>
     <row r="601" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B601" s="6" t="str">
+      <c r="B601" s="6">
         <f>IF(EXACT([1]MAIN!$F599, ""), "", [1]MAIN!$F599)</f>
-        <v/>
+        <v>4000000000596</v>
       </c>
       <c r="C601" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F599, ""), "", [1]MAIN!$B599)</f>
-        <v/>
+        <v>(LDAP) taufiq.aminudin</v>
       </c>
       <c r="D601" s="2"/>
       <c r="E601" s="2"/>
@@ -19844,13 +20033,13 @@
       <c r="H601" s="5"/>
     </row>
     <row r="602" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B602" s="6" t="str">
+      <c r="B602" s="6">
         <f>IF(EXACT([1]MAIN!$F600, ""), "", [1]MAIN!$F600)</f>
-        <v/>
+        <v>4000000000597</v>
       </c>
       <c r="C602" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F600, ""), "", [1]MAIN!$B600)</f>
-        <v/>
+        <v>(LDAP) risty.alawiyah</v>
       </c>
       <c r="D602" s="2"/>
       <c r="E602" s="2"/>
@@ -19858,13 +20047,13 @@
       <c r="H602" s="5"/>
     </row>
     <row r="603" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B603" s="6" t="str">
+      <c r="B603" s="6">
         <f>IF(EXACT([1]MAIN!$F601, ""), "", [1]MAIN!$F601)</f>
-        <v/>
+        <v>4000000000598</v>
       </c>
       <c r="C603" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F601, ""), "", [1]MAIN!$B601)</f>
-        <v/>
+        <v>(LDAP) agus.sobar</v>
       </c>
       <c r="D603" s="2"/>
       <c r="E603" s="2"/>
@@ -19872,13 +20061,13 @@
       <c r="H603" s="5"/>
     </row>
     <row r="604" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B604" s="6" t="str">
+      <c r="B604" s="6">
         <f>IF(EXACT([1]MAIN!$F602, ""), "", [1]MAIN!$F602)</f>
-        <v/>
+        <v>4000000000599</v>
       </c>
       <c r="C604" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F602, ""), "", [1]MAIN!$B602)</f>
-        <v/>
+        <v>(LDAP) reza.sanjaya</v>
       </c>
       <c r="D604" s="2"/>
       <c r="E604" s="2"/>
@@ -19886,13 +20075,13 @@
       <c r="H604" s="5"/>
     </row>
     <row r="605" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B605" s="6" t="str">
+      <c r="B605" s="6">
         <f>IF(EXACT([1]MAIN!$F603, ""), "", [1]MAIN!$F603)</f>
-        <v/>
+        <v>4000000000600</v>
       </c>
       <c r="C605" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F603, ""), "", [1]MAIN!$B603)</f>
-        <v/>
+        <v>(LDAP) kiki.prasetyo</v>
       </c>
       <c r="D605" s="2"/>
       <c r="E605" s="2"/>
@@ -19900,13 +20089,13 @@
       <c r="H605" s="5"/>
     </row>
     <row r="606" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B606" s="6" t="str">
+      <c r="B606" s="6">
         <f>IF(EXACT([1]MAIN!$F604, ""), "", [1]MAIN!$F604)</f>
-        <v/>
+        <v>4000000000601</v>
       </c>
       <c r="C606" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F604, ""), "", [1]MAIN!$B604)</f>
-        <v/>
+        <v>(LDAP) ulul.azmi</v>
       </c>
       <c r="D606" s="2"/>
       <c r="E606" s="2"/>
@@ -19914,13 +20103,13 @@
       <c r="H606" s="5"/>
     </row>
     <row r="607" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B607" s="6" t="str">
+      <c r="B607" s="6">
         <f>IF(EXACT([1]MAIN!$F605, ""), "", [1]MAIN!$F605)</f>
-        <v/>
+        <v>4000000000602</v>
       </c>
       <c r="C607" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F605, ""), "", [1]MAIN!$B605)</f>
-        <v/>
+        <v>(LDAP) arie.gustaman</v>
       </c>
       <c r="D607" s="2"/>
       <c r="E607" s="2"/>
@@ -19928,13 +20117,13 @@
       <c r="H607" s="5"/>
     </row>
     <row r="608" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B608" s="6" t="str">
+      <c r="B608" s="6">
         <f>IF(EXACT([1]MAIN!$F606, ""), "", [1]MAIN!$F606)</f>
-        <v/>
+        <v>4000000000603</v>
       </c>
       <c r="C608" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F606, ""), "", [1]MAIN!$B606)</f>
-        <v/>
+        <v>(LDAP) zulfikar.siregar</v>
       </c>
       <c r="D608" s="2"/>
       <c r="E608" s="2"/>
@@ -19942,13 +20131,13 @@
       <c r="H608" s="5"/>
     </row>
     <row r="609" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B609" s="6" t="str">
+      <c r="B609" s="6">
         <f>IF(EXACT([1]MAIN!$F607, ""), "", [1]MAIN!$F607)</f>
-        <v/>
+        <v>4000000000604</v>
       </c>
       <c r="C609" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F607, ""), "", [1]MAIN!$B607)</f>
-        <v/>
+        <v>(LDAP) deby.syahputra</v>
       </c>
       <c r="D609" s="2"/>
       <c r="E609" s="2"/>
@@ -19956,13 +20145,13 @@
       <c r="H609" s="5"/>
     </row>
     <row r="610" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B610" s="6" t="str">
+      <c r="B610" s="6">
         <f>IF(EXACT([1]MAIN!$F608, ""), "", [1]MAIN!$F608)</f>
-        <v/>
+        <v>4000000000605</v>
       </c>
       <c r="C610" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F608, ""), "", [1]MAIN!$B608)</f>
-        <v/>
+        <v>(LDAP) Risaldi</v>
       </c>
       <c r="D610" s="2"/>
       <c r="E610" s="2"/>
@@ -19970,13 +20159,13 @@
       <c r="H610" s="5"/>
     </row>
     <row r="611" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B611" s="6" t="str">
+      <c r="B611" s="6">
         <f>IF(EXACT([1]MAIN!$F609, ""), "", [1]MAIN!$F609)</f>
-        <v/>
+        <v>4000000000606</v>
       </c>
       <c r="C611" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F609, ""), "", [1]MAIN!$B609)</f>
-        <v/>
+        <v>(LDAP) muhammad.hairul</v>
       </c>
       <c r="D611" s="2"/>
       <c r="E611" s="2"/>
@@ -19984,13 +20173,13 @@
       <c r="H611" s="5"/>
     </row>
     <row r="612" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B612" s="6" t="str">
+      <c r="B612" s="6">
         <f>IF(EXACT([1]MAIN!$F610, ""), "", [1]MAIN!$F610)</f>
-        <v/>
+        <v>4000000000607</v>
       </c>
       <c r="C612" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F610, ""), "", [1]MAIN!$B610)</f>
-        <v/>
+        <v>(LDAP) ibrahim.arya</v>
       </c>
       <c r="D612" s="2"/>
       <c r="E612" s="2"/>
@@ -19998,13 +20187,13 @@
       <c r="H612" s="5"/>
     </row>
     <row r="613" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B613" s="6" t="str">
+      <c r="B613" s="6">
         <f>IF(EXACT([1]MAIN!$F611, ""), "", [1]MAIN!$F611)</f>
-        <v/>
+        <v>4000000000608</v>
       </c>
       <c r="C613" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F611, ""), "", [1]MAIN!$B611)</f>
-        <v/>
+        <v>(LDAP) m.bilal</v>
       </c>
       <c r="D613" s="2"/>
       <c r="E613" s="2"/>
@@ -20012,13 +20201,13 @@
       <c r="H613" s="5"/>
     </row>
     <row r="614" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B614" s="6" t="str">
+      <c r="B614" s="6">
         <f>IF(EXACT([1]MAIN!$F612, ""), "", [1]MAIN!$F612)</f>
-        <v/>
+        <v>4000000000609</v>
       </c>
       <c r="C614" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F612, ""), "", [1]MAIN!$B612)</f>
-        <v/>
+        <v>(LDAP) jamil</v>
       </c>
       <c r="D614" s="2"/>
       <c r="E614" s="2"/>
@@ -20026,13 +20215,13 @@
       <c r="H614" s="5"/>
     </row>
     <row r="615" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B615" s="6" t="str">
+      <c r="B615" s="6">
         <f>IF(EXACT([1]MAIN!$F613, ""), "", [1]MAIN!$F613)</f>
-        <v/>
+        <v>4000000000610</v>
       </c>
       <c r="C615" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F613, ""), "", [1]MAIN!$B613)</f>
-        <v/>
+        <v>(LDAP) wiyadianto</v>
       </c>
       <c r="D615" s="2"/>
       <c r="E615" s="2"/>
@@ -20040,13 +20229,13 @@
       <c r="H615" s="5"/>
     </row>
     <row r="616" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B616" s="6" t="str">
+      <c r="B616" s="6">
         <f>IF(EXACT([1]MAIN!$F614, ""), "", [1]MAIN!$F614)</f>
-        <v/>
+        <v>4000000000611</v>
       </c>
       <c r="C616" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F614, ""), "", [1]MAIN!$B614)</f>
-        <v/>
+        <v>(LDAP) rahmad.dwifar</v>
       </c>
       <c r="D616" s="2"/>
       <c r="E616" s="2"/>
@@ -20054,13 +20243,13 @@
       <c r="H616" s="5"/>
     </row>
     <row r="617" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B617" s="6" t="str">
+      <c r="B617" s="6">
         <f>IF(EXACT([1]MAIN!$F615, ""), "", [1]MAIN!$F615)</f>
-        <v/>
+        <v>4000000000612</v>
       </c>
       <c r="C617" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F615, ""), "", [1]MAIN!$B615)</f>
-        <v/>
+        <v>(LDAP) achmad.sandi</v>
       </c>
       <c r="D617" s="2"/>
       <c r="E617" s="2"/>
@@ -20068,13 +20257,13 @@
       <c r="H617" s="5"/>
     </row>
     <row r="618" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B618" s="6" t="str">
+      <c r="B618" s="6">
         <f>IF(EXACT([1]MAIN!$F616, ""), "", [1]MAIN!$F616)</f>
-        <v/>
+        <v>4000000000613</v>
       </c>
       <c r="C618" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F616, ""), "", [1]MAIN!$B616)</f>
-        <v/>
+        <v>(LDAP) andrean.fahrizi</v>
       </c>
       <c r="D618" s="2"/>
       <c r="E618" s="2"/>
@@ -20082,13 +20271,13 @@
       <c r="H618" s="5"/>
     </row>
     <row r="619" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B619" s="6" t="str">
+      <c r="B619" s="6">
         <f>IF(EXACT([1]MAIN!$F617, ""), "", [1]MAIN!$F617)</f>
-        <v/>
+        <v>4000000000614</v>
       </c>
       <c r="C619" s="6" t="str">
         <f>IF(EXACT([1]MAIN!$F617, ""), "", [1]MAIN!$B617)</f>
-        <v/>
+        <v>(LDAP) amar.abdilah</v>
       </c>
       <c r="D619" s="2"/>
       <c r="E619" s="2"/>
@@ -20096,13 +20285,13 @@
       <c r="H619" s="5"/>
     </row>
     <row r="620" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B620" s="6" t="str">
+      <c r="B620" s="6">
         <f>IF(EXACT([1]MAIN!$F618, ""), "", [1]MAIN!$F618)</f>
-        <v/>
-      </c>
-      <c r="C620" s="6" t="str">
+        <v>4000000000614</v>
+      </c>
+      <c r="C620" s="6">
         <f>IF(EXACT([1]MAIN!$F618, ""), "", [1]MAIN!$B618)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D620" s="2"/>
       <c r="E620" s="2"/>
